--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/25gps/5mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/25gps/5mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.63396340278</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>704.2517940566099</v>
       </c>
-      <c r="W2" t="b">
-        <v>0</v>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
       <c r="X2">
-        <v>707.1044033795463</v>
+        <v>0.249934488</v>
+      </c>
+      <c r="Y2">
+        <v>0.2626676</v>
+      </c>
+      <c r="Z2">
+        <v>0.3625762214784392</v>
+      </c>
+      <c r="AA2">
+        <v>6.366555999999996</v>
+      </c>
+      <c r="AB2">
+        <v>0.05782143060354774</v>
+      </c>
+      <c r="AC2">
+        <v>40.72084623746827</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.63407914352</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>707.6669996695475</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>706.6771224569081</v>
+      </c>
+      <c r="X3">
+        <v>0.2499383</v>
+      </c>
+      <c r="Y3">
+        <v>0.262656778</v>
+      </c>
+      <c r="Z3">
+        <v>0.3625710093708973</v>
+      </c>
+      <c r="AA3">
+        <v>6.359239000000002</v>
+      </c>
+      <c r="AB3">
+        <v>0.05788516436818718</v>
+      </c>
+      <c r="AC3">
+        <v>40.96342059381362</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.63419546296</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>705.2907608627235</v>
       </c>
-      <c r="V4">
-        <v>1.750694732094612</v>
-      </c>
-      <c r="W4" t="b">
+      <c r="V4" t="b">
         <v>1</v>
       </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.249916694</v>
+      </c>
+      <c r="Y4">
+        <v>0.262641814</v>
+      </c>
+      <c r="Z4">
+        <v>0.3625452749672793</v>
+      </c>
+      <c r="AA4">
+        <v>6.362559999999995</v>
+      </c>
+      <c r="AB4">
+        <v>0.05785186880590133</v>
+      </c>
+      <c r="AC4">
+        <v>40.8023885674446</v>
+      </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.63431120371</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>707.956614110635</v>
       </c>
-      <c r="V5">
-        <v>1.462712145920634</v>
-      </c>
-      <c r="W5" t="b">
+      <c r="V5" t="b">
         <v>1</v>
       </c>
+      <c r="W5">
+        <v>40.86913635645752</v>
+      </c>
+      <c r="X5">
+        <v>0.249908114</v>
+      </c>
+      <c r="Y5">
+        <v>0.262637994</v>
+      </c>
+      <c r="Z5">
+        <v>0.3625365930983809</v>
+      </c>
+      <c r="AA5">
+        <v>6.364940000000004</v>
+      </c>
+      <c r="AB5">
+        <v>0.0578295396354485</v>
+      </c>
+      <c r="AC5">
+        <v>40.94080507588888</v>
+      </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.63442752315</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>706.4994123684789</v>
       </c>
-      <c r="V6">
-        <v>1.334856354263595</v>
-      </c>
-      <c r="W6" t="b">
+      <c r="V6" t="b">
         <v>1</v>
       </c>
+      <c r="X6">
+        <v>0.24990462</v>
+      </c>
+      <c r="Y6">
+        <v>0.262631946</v>
+      </c>
+      <c r="Z6">
+        <v>0.3625298031294687</v>
+      </c>
+      <c r="AA6">
+        <v>6.363663000000003</v>
+      </c>
+      <c r="AB6">
+        <v>0.05783974643036858</v>
+      </c>
+      <c r="AC6">
+        <v>40.86374686459722</v>
+      </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.63454384259</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>705.4061872149889</v>
       </c>
-      <c r="V7">
-        <v>1.279534778972404</v>
-      </c>
-      <c r="W7" t="b">
+      <c r="V7" t="b">
         <v>1</v>
       </c>
+      <c r="X7">
+        <v>0.249907162</v>
+      </c>
+      <c r="Y7">
+        <v>0.262622078</v>
+      </c>
+      <c r="Z7">
+        <v>0.3625244067258538</v>
+      </c>
+      <c r="AA7">
+        <v>6.357458000000001</v>
+      </c>
+      <c r="AB7">
+        <v>0.05789367639599852</v>
+      </c>
+      <c r="AC7">
+        <v>40.83855753035972</v>
+      </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.63465958333</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>708.6275780261367</v>
       </c>
-      <c r="V8">
-        <v>1.638169153903376</v>
-      </c>
-      <c r="W8" t="b">
+      <c r="V8" t="b">
         <v>1</v>
       </c>
+      <c r="X8">
+        <v>0.249895406</v>
+      </c>
+      <c r="Y8">
+        <v>0.262624624</v>
+      </c>
+      <c r="Z8">
+        <v>0.3625181472299644</v>
+      </c>
+      <c r="AA8">
+        <v>6.364609000000002</v>
+      </c>
+      <c r="AB8">
+        <v>0.0578296026738494</v>
+      </c>
+      <c r="AC8">
+        <v>40.9796512809837</v>
+      </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.63477590278</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>705.9795665955188</v>
       </c>
-      <c r="V9">
-        <v>1.718433744666249</v>
-      </c>
-      <c r="W9" t="b">
+      <c r="V9" t="b">
         <v>1</v>
       </c>
+      <c r="X9">
+        <v>0.24989318</v>
+      </c>
+      <c r="Y9">
+        <v>0.262618258</v>
+      </c>
+      <c r="Z9">
+        <v>0.3625120009675086</v>
+      </c>
+      <c r="AA9">
+        <v>6.362538999999998</v>
+      </c>
+      <c r="AB9">
+        <v>0.0578469030991756</v>
+      </c>
+      <c r="AC9">
+        <v>40.83873157884896</v>
+      </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.63489164352</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>708.2079565524322</v>
       </c>
-      <c r="V10">
-        <v>1.423245617005213</v>
-      </c>
-      <c r="W10" t="b">
+      <c r="V10" t="b">
         <v>1</v>
       </c>
+      <c r="X10">
+        <v>0.24988492</v>
+      </c>
+      <c r="Y10">
+        <v>0.262605842</v>
+      </c>
+      <c r="Z10">
+        <v>0.3624973123982236</v>
+      </c>
+      <c r="AA10">
+        <v>6.360461000000001</v>
+      </c>
+      <c r="AB10">
+        <v>0.05786296272647676</v>
+      </c>
+      <c r="AC10">
+        <v>40.97901059258766</v>
+      </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.63500738426</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>707.2656767869083</v>
       </c>
-      <c r="V11">
-        <v>1.118607198035578</v>
-      </c>
-      <c r="W11" t="b">
+      <c r="V11" t="b">
         <v>1</v>
       </c>
+      <c r="X11">
+        <v>0.249876976</v>
+      </c>
+      <c r="Y11">
+        <v>0.262605842</v>
+      </c>
+      <c r="Z11">
+        <v>0.3624918363045346</v>
+      </c>
+      <c r="AA11">
+        <v>6.364432999999998</v>
+      </c>
+      <c r="AB11">
+        <v>0.05782708227848021</v>
+      </c>
+      <c r="AC11">
+        <v>40.89911048430154</v>
+      </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.635123125</v>
       </c>
@@ -1269,14 +1470,29 @@
       <c r="U12">
         <v>706.5851443983155</v>
       </c>
-      <c r="V12">
-        <v>0.8149166394982087</v>
-      </c>
-      <c r="W12" t="b">
+      <c r="V12" t="b">
         <v>1</v>
       </c>
+      <c r="X12">
+        <v>0.249871574</v>
+      </c>
+      <c r="Y12">
+        <v>0.262604886</v>
+      </c>
+      <c r="Z12">
+        <v>0.3624874199807636</v>
+      </c>
+      <c r="AA12">
+        <v>6.366655999999999</v>
+      </c>
+      <c r="AB12">
+        <v>0.05780681190808495</v>
+      </c>
+      <c r="AC12">
+        <v>40.84543453928047</v>
+      </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>46068.63523944445</v>
       </c>
@@ -1340,14 +1556,29 @@
       <c r="U13">
         <v>708.6976091586579</v>
       </c>
-      <c r="V13">
-        <v>1.078275012297766</v>
-      </c>
-      <c r="W13" t="b">
+      <c r="V13" t="b">
         <v>1</v>
       </c>
+      <c r="X13">
+        <v>0.24986109</v>
+      </c>
+      <c r="Y13">
+        <v>0.262602976</v>
+      </c>
+      <c r="Z13">
+        <v>0.3624788094496624</v>
+      </c>
+      <c r="AA13">
+        <v>6.370942999999997</v>
+      </c>
+      <c r="AB13">
+        <v>0.05776774707250792</v>
+      </c>
+      <c r="AC13">
+        <v>40.93986423676842</v>
+      </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:29">
       <c r="A14" s="1">
         <v>46068.63535518519</v>
       </c>
@@ -1411,11 +1642,26 @@
       <c r="U14">
         <v>704.3672921388538</v>
       </c>
-      <c r="V14">
-        <v>2.165372235147606</v>
-      </c>
-      <c r="W14" t="b">
+      <c r="V14" t="b">
         <v>1</v>
+      </c>
+      <c r="X14">
+        <v>0.249863632</v>
+      </c>
+      <c r="Y14">
+        <v>0.262606478</v>
+      </c>
+      <c r="Z14">
+        <v>0.3624830987560604</v>
+      </c>
+      <c r="AA14">
+        <v>6.371423</v>
+      </c>
+      <c r="AB14">
+        <v>0.05776418852166673</v>
+      </c>
+      <c r="AC14">
+        <v>40.68720505160466</v>
       </c>
     </row>
   </sheetData>
